--- a/artfynd/A 39623-2026 artfynd.xlsx
+++ b/artfynd/A 39623-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ17"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2411,6 +2411,228 @@
       <c r="AZ17" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/112646543</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>136858377</v>
+      </c>
+      <c r="B18" t="n">
+        <v>93449</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Riddarhyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>528049</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6629530</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136858377</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>136858379</v>
+      </c>
+      <c r="B19" t="n">
+        <v>5485</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>101920</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Raggbock</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Tragosoma depsarium</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1767)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Riddarhyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>528046</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6629440</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136858379</t>
         </is>
       </c>
     </row>
@@ -2432,6 +2654,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39623-2026 artfynd.xlsx
+++ b/artfynd/A 39623-2026 artfynd.xlsx
@@ -2419,7 +2419,7 @@
         <v>136858377</v>
       </c>
       <c r="B18" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 39623-2026 artfynd.xlsx
+++ b/artfynd/A 39623-2026 artfynd.xlsx
@@ -2419,7 +2419,7 @@
         <v>136858377</v>
       </c>
       <c r="B18" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 39623-2026 artfynd.xlsx
+++ b/artfynd/A 39623-2026 artfynd.xlsx
@@ -2419,7 +2419,7 @@
         <v>136858377</v>
       </c>
       <c r="B18" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 39623-2026 artfynd.xlsx
+++ b/artfynd/A 39623-2026 artfynd.xlsx
@@ -2419,7 +2419,7 @@
         <v>136858377</v>
       </c>
       <c r="B18" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 39623-2026 artfynd.xlsx
+++ b/artfynd/A 39623-2026 artfynd.xlsx
@@ -2419,7 +2419,7 @@
         <v>136858377</v>
       </c>
       <c r="B18" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 39623-2026 artfynd.xlsx
+++ b/artfynd/A 39623-2026 artfynd.xlsx
@@ -2419,7 +2419,7 @@
         <v>136858377</v>
       </c>
       <c r="B18" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 39623-2026 artfynd.xlsx
+++ b/artfynd/A 39623-2026 artfynd.xlsx
@@ -2419,7 +2419,7 @@
         <v>136858377</v>
       </c>
       <c r="B18" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 39623-2026 artfynd.xlsx
+++ b/artfynd/A 39623-2026 artfynd.xlsx
@@ -2419,7 +2419,7 @@
         <v>136858377</v>
       </c>
       <c r="B18" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 39623-2026 artfynd.xlsx
+++ b/artfynd/A 39623-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ19"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2419,7 +2419,7 @@
         <v>136858377</v>
       </c>
       <c r="B18" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,32 +2527,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136858379</v>
+        <v>137282836</v>
       </c>
       <c r="B19" t="n">
-        <v>5485</v>
+        <v>93483</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>101920</v>
+        <v>5966</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -2562,17 +2562,17 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Riddarhyttan, Vstm</t>
+          <t>Forshammar, Vstm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>528046</v>
+        <v>527998</v>
       </c>
       <c r="R19" t="n">
-        <v>6629440</v>
+        <v>6629288</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2596,12 +2596,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2632,7 +2642,360 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/137282836</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>136858379</v>
+      </c>
+      <c r="B20" t="n">
+        <v>5485</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>101920</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Raggbock</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Tragosoma depsarium</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1767)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Riddarhyttan, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>528046</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6629440</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/136858379</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>137282768</v>
+      </c>
+      <c r="B21" t="n">
+        <v>107905</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>219686</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Vätteros</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lathraea squamaria</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Forshammar, Vstm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>528001</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6629285</v>
+      </c>
+      <c r="S21" t="n">
+        <v>5</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>11:07</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137282768</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>137282816</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98256</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Forshammar, Vstm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>528069</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6629388</v>
+      </c>
+      <c r="S22" t="n">
+        <v>5</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Skinnskatteberg</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/137282816</t>
         </is>
       </c>
     </row>
@@ -2656,6 +3019,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39623-2026 artfynd.xlsx
+++ b/artfynd/A 39623-2026 artfynd.xlsx
@@ -2419,7 +2419,7 @@
         <v>136858377</v>
       </c>
       <c r="B18" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>137282836</v>
       </c>
       <c r="B19" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2651,7 +2651,7 @@
         <v>136858379</v>
       </c>
       <c r="B20" t="n">
-        <v>5485</v>
+        <v>5491</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>137282768</v>
       </c>
       <c r="B21" t="n">
-        <v>107905</v>
+        <v>107926</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>137282816</v>
       </c>
       <c r="B22" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 39623-2026 artfynd.xlsx
+++ b/artfynd/A 39623-2026 artfynd.xlsx
@@ -2419,7 +2419,7 @@
         <v>136858377</v>
       </c>
       <c r="B18" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>137282836</v>
       </c>
       <c r="B19" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>137282768</v>
       </c>
       <c r="B21" t="n">
-        <v>107926</v>
+        <v>107927</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>137282816</v>
       </c>
       <c r="B22" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 39623-2026 artfynd.xlsx
+++ b/artfynd/A 39623-2026 artfynd.xlsx
@@ -2419,7 +2419,7 @@
         <v>136858377</v>
       </c>
       <c r="B18" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>137282836</v>
       </c>
       <c r="B19" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>137282768</v>
       </c>
       <c r="B21" t="n">
-        <v>107927</v>
+        <v>107932</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>137282816</v>
       </c>
       <c r="B22" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 39623-2026 artfynd.xlsx
+++ b/artfynd/A 39623-2026 artfynd.xlsx
@@ -2419,7 +2419,7 @@
         <v>136858377</v>
       </c>
       <c r="B18" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>137282836</v>
       </c>
       <c r="B19" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>137282768</v>
       </c>
       <c r="B21" t="n">
-        <v>107932</v>
+        <v>107935</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>137282816</v>
       </c>
       <c r="B22" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 39623-2026 artfynd.xlsx
+++ b/artfynd/A 39623-2026 artfynd.xlsx
@@ -2419,7 +2419,7 @@
         <v>136858377</v>
       </c>
       <c r="B18" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>137282836</v>
       </c>
       <c r="B19" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>137282768</v>
       </c>
       <c r="B21" t="n">
-        <v>107935</v>
+        <v>107941</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>137282816</v>
       </c>
       <c r="B22" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 39623-2026 artfynd.xlsx
+++ b/artfynd/A 39623-2026 artfynd.xlsx
@@ -2762,7 +2762,7 @@
         <v>137282768</v>
       </c>
       <c r="B21" t="n">
-        <v>107941</v>
+        <v>107942</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 39623-2026 artfynd.xlsx
+++ b/artfynd/A 39623-2026 artfynd.xlsx
@@ -2419,7 +2419,7 @@
         <v>136858377</v>
       </c>
       <c r="B18" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
         <v>137282836</v>
       </c>
       <c r="B19" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>137282768</v>
       </c>
       <c r="B21" t="n">
-        <v>107942</v>
+        <v>107954</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>137282816</v>
       </c>
       <c r="B22" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 39623-2026 artfynd.xlsx
+++ b/artfynd/A 39623-2026 artfynd.xlsx
@@ -2530,7 +2530,7 @@
         <v>137282836</v>
       </c>
       <c r="B19" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>137282768</v>
       </c>
       <c r="B21" t="n">
-        <v>107954</v>
+        <v>107955</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>137282816</v>
       </c>
       <c r="B22" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 39623-2026 artfynd.xlsx
+++ b/artfynd/A 39623-2026 artfynd.xlsx
@@ -2530,7 +2530,7 @@
         <v>137282836</v>
       </c>
       <c r="B19" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>137282768</v>
       </c>
       <c r="B21" t="n">
-        <v>107955</v>
+        <v>107958</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>137282816</v>
       </c>
       <c r="B22" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 39623-2026 artfynd.xlsx
+++ b/artfynd/A 39623-2026 artfynd.xlsx
@@ -2530,7 +2530,7 @@
         <v>137282836</v>
       </c>
       <c r="B19" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2762,7 +2762,7 @@
         <v>137282768</v>
       </c>
       <c r="B21" t="n">
-        <v>107958</v>
+        <v>107964</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
         <v>137282816</v>
       </c>
       <c r="B22" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
